--- a/supporting_material/experiments/favalli/lane-2.xlsx
+++ b/supporting_material/experiments/favalli/lane-2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adrianomartinelli/projects/delt-hit/supporting_material/experiments/favalli/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F068970F-5634-FE4C-8C0E-14FEAC5D4A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825494E8-EF8D-E64D-A95B-D2060B430C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="660" windowWidth="15120" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10600" yWindow="660" windowWidth="15120" windowHeight="18980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="experiment" sheetId="8" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="1469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2008" uniqueCount="1520">
   <si>
     <t>GCCTCG</t>
   </si>
@@ -4451,13 +4451,166 @@
   </si>
   <si>
     <t>./20190812.A-1907_NF2GB2_s2_R1.fastq.gz</t>
+  </si>
+  <si>
+    <t>CAIX_ss</t>
+  </si>
+  <si>
+    <t>protein</t>
+  </si>
+  <si>
+    <t>CAIX_ds</t>
+  </si>
+  <si>
+    <t>CAIX_2+1</t>
+  </si>
+  <si>
+    <t>CAIX_2+2</t>
+  </si>
+  <si>
+    <t>CAIX_2+3</t>
+  </si>
+  <si>
+    <t>No prot_ss</t>
+  </si>
+  <si>
+    <t>no_protein</t>
+  </si>
+  <si>
+    <t>albumin_ss</t>
+  </si>
+  <si>
+    <t>albumin_ds</t>
+  </si>
+  <si>
+    <t>albumin_2+1</t>
+  </si>
+  <si>
+    <t>albumin_2+2</t>
+  </si>
+  <si>
+    <t>albumin_2+3</t>
+  </si>
+  <si>
+    <t>No prot_ds</t>
+  </si>
+  <si>
+    <t>L19-IL-12_ss</t>
+  </si>
+  <si>
+    <t>CREBBP_ss</t>
+  </si>
+  <si>
+    <t>CREBBP_ds</t>
+  </si>
+  <si>
+    <t>CREBBP_s2+1</t>
+  </si>
+  <si>
+    <t>CREBBP_s2+2</t>
+  </si>
+  <si>
+    <t>CREBBP_s2+3</t>
+  </si>
+  <si>
+    <t>L19-IL2_ss</t>
+  </si>
+  <si>
+    <t>L19-IL2_ds</t>
+  </si>
+  <si>
+    <t>L19-IL2_2+1_L</t>
+  </si>
+  <si>
+    <t>L19-IL2_2+1_D</t>
+  </si>
+  <si>
+    <t>Tyrp-1_ss</t>
+  </si>
+  <si>
+    <t>Tyrp-1_ds</t>
+  </si>
+  <si>
+    <t>Tyrp-1_2+1</t>
+  </si>
+  <si>
+    <t>tyros_ss</t>
+  </si>
+  <si>
+    <t>tyros_ds</t>
+  </si>
+  <si>
+    <t>tyros_2+1</t>
+  </si>
+  <si>
+    <t>bASSA-c013 2uM_ss</t>
+  </si>
+  <si>
+    <t>bASSA-c013 2uM_ds</t>
+  </si>
+  <si>
+    <t>L19-IL12_ds</t>
+  </si>
+  <si>
+    <t>IL12-receptor_ss</t>
+  </si>
+  <si>
+    <t>IL12-receptor_ds</t>
+  </si>
+  <si>
+    <t>bSGF29_ss</t>
+  </si>
+  <si>
+    <t>bSGF29_ds</t>
+  </si>
+  <si>
+    <t>bRBBP4_ss</t>
+  </si>
+  <si>
+    <t>bRBBP4_ds</t>
+  </si>
+  <si>
+    <t>WT CTIP_ss</t>
+  </si>
+  <si>
+    <t>WT CTIP_ds</t>
+  </si>
+  <si>
+    <t>L27E CTIP_ss</t>
+  </si>
+  <si>
+    <t>L27E CTIP_ds</t>
+  </si>
+  <si>
+    <t>FAN1_ss</t>
+  </si>
+  <si>
+    <t>FAN1_ds</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>beads</t>
+  </si>
+  <si>
+    <t>No Protein</t>
+  </si>
+  <si>
+    <t>HisPURE Beads</t>
+  </si>
+  <si>
+    <t>Dynabeads SA C1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4526,13 +4679,56 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B9BD5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="20">
@@ -4796,7 +4992,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4865,6 +5061,30 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5116,15 +5336,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9286309-5176-CB48-AB9B-E8EF56CF21B1}">
-  <dimension ref="A1:C517"/>
+  <dimension ref="A1:F517"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="34" t="s">
         <v>14</v>
       </c>
@@ -5134,8 +5357,17 @@
       <c r="C1" s="18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D1" s="42" t="s">
+        <v>1514</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
         <v>975</v>
       </c>
@@ -5145,8 +5377,17 @@
       <c r="C2" s="18" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" s="43" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F2" s="44" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="18" t="s">
         <v>976</v>
       </c>
@@ -5156,8 +5397,17 @@
       <c r="C3" s="18" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D3" s="43" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F3" s="44" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="18" t="s">
         <v>979</v>
       </c>
@@ -5167,8 +5417,17 @@
       <c r="C4" s="18" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4" s="43" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
         <v>981</v>
       </c>
@@ -5178,8 +5437,17 @@
       <c r="C5" s="18" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D5" s="45" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F5" s="46" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
         <v>982</v>
       </c>
@@ -5189,8 +5457,17 @@
       <c r="C6" s="18" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D6" s="45" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
         <v>983</v>
       </c>
@@ -5200,8 +5477,17 @@
       <c r="C7" s="18" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D7" s="45" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
         <v>984</v>
       </c>
@@ -5212,7 +5498,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="18" t="s">
         <v>985</v>
       </c>
@@ -5223,7 +5509,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
         <v>986</v>
       </c>
@@ -5234,7 +5520,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
         <v>987</v>
       </c>
@@ -5245,7 +5531,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="18" t="s">
         <v>988</v>
       </c>
@@ -5256,7 +5542,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
         <v>989</v>
       </c>
@@ -5267,7 +5553,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
         <v>990</v>
       </c>
@@ -5278,7 +5564,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
         <v>991</v>
       </c>
@@ -5289,7 +5575,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="18" t="s">
         <v>992</v>
       </c>
@@ -5773,7 +6059,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="18" t="s">
         <v>1036</v>
       </c>
@@ -6180,7 +6466,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="18" t="s">
         <v>1073</v>
       </c>
@@ -6191,7 +6477,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="18" t="s">
         <v>977</v>
       </c>
@@ -6201,8 +6487,14 @@
       <c r="C98" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D98" s="41" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E98" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="18" t="s">
         <v>978</v>
       </c>
@@ -6212,8 +6504,14 @@
       <c r="C99" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D99" s="41" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E99" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="18" t="s">
         <v>980</v>
       </c>
@@ -6223,8 +6521,14 @@
       <c r="C100" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D100" s="41" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E100" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="18" t="s">
         <v>1074</v>
       </c>
@@ -6234,8 +6538,14 @@
       <c r="C101" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D101" s="41" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E101" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="18" t="s">
         <v>1075</v>
       </c>
@@ -6245,8 +6555,14 @@
       <c r="C102" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D102" s="41" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E102" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="18" t="s">
         <v>1076</v>
       </c>
@@ -6256,8 +6572,14 @@
       <c r="C103" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D103" s="41" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E103" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="18" t="s">
         <v>1077</v>
       </c>
@@ -6267,8 +6589,14 @@
       <c r="C104" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D104" s="41" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E104" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="18" t="s">
         <v>1078</v>
       </c>
@@ -6278,8 +6606,14 @@
       <c r="C105" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D105" s="41" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E105" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="18" t="s">
         <v>1079</v>
       </c>
@@ -6289,8 +6623,14 @@
       <c r="C106" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D106" s="41" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E106" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="18" t="s">
         <v>1080</v>
       </c>
@@ -6300,8 +6640,14 @@
       <c r="C107" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D107" s="41" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E107" s="40" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="18" t="s">
         <v>1081</v>
       </c>
@@ -6311,8 +6657,14 @@
       <c r="C108" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D108" s="41" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E108" s="40" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="18" t="s">
         <v>1082</v>
       </c>
@@ -6322,8 +6674,14 @@
       <c r="C109" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D109" s="41" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E109" s="40" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="18" t="s">
         <v>1083</v>
       </c>
@@ -6333,8 +6691,14 @@
       <c r="C110" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D110" s="41" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E110" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="18" t="s">
         <v>1084</v>
       </c>
@@ -6344,8 +6708,14 @@
       <c r="C111" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D111" s="41" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E111" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" s="18" t="s">
         <v>1085</v>
       </c>
@@ -6355,8 +6725,14 @@
       <c r="C112" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D112" s="41" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E112" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="18" t="s">
         <v>1086</v>
       </c>
@@ -6366,8 +6742,14 @@
       <c r="C113" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D113" s="41" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E113" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="18" t="s">
         <v>1087</v>
       </c>
@@ -6377,8 +6759,14 @@
       <c r="C114" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D114" s="41" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E114" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="18" t="s">
         <v>1088</v>
       </c>
@@ -6388,8 +6776,14 @@
       <c r="C115" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D115" s="41" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E115" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="18" t="s">
         <v>1089</v>
       </c>
@@ -6399,8 +6793,14 @@
       <c r="C116" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D116" s="41" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E116" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="18" t="s">
         <v>1090</v>
       </c>
@@ -6410,8 +6810,14 @@
       <c r="C117" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D117" s="41" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E117" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="18" t="s">
         <v>1091</v>
       </c>
@@ -6421,8 +6827,14 @@
       <c r="C118" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D118" s="41" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E118" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="18" t="s">
         <v>1092</v>
       </c>
@@ -6432,8 +6844,14 @@
       <c r="C119" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D119" s="41" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E119" s="40" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="18" t="s">
         <v>1093</v>
       </c>
@@ -6443,8 +6861,14 @@
       <c r="C120" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D120" s="41" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E120" s="40" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="18" t="s">
         <v>1094</v>
       </c>
@@ -6454,8 +6878,14 @@
       <c r="C121" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D121" s="41" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E121" s="40" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="18" t="s">
         <v>1095</v>
       </c>
@@ -6465,8 +6895,14 @@
       <c r="C122" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D122" s="41" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E122" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="18" t="s">
         <v>1096</v>
       </c>
@@ -6476,8 +6912,14 @@
       <c r="C123" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D123" s="41" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E123" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="18" t="s">
         <v>1097</v>
       </c>
@@ -6487,8 +6929,14 @@
       <c r="C124" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D124" s="41" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E124" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="18" t="s">
         <v>1098</v>
       </c>
@@ -6498,8 +6946,14 @@
       <c r="C125" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D125" s="41" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E125" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="18" t="s">
         <v>1099</v>
       </c>
@@ -6509,8 +6963,14 @@
       <c r="C126" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D126" s="41" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E126" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="18" t="s">
         <v>1100</v>
       </c>
@@ -6520,8 +6980,14 @@
       <c r="C127" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D127" s="41" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E127" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="18" t="s">
         <v>1101</v>
       </c>
@@ -6531,8 +6997,14 @@
       <c r="C128" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D128" s="41" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E128" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="18" t="s">
         <v>1102</v>
       </c>
@@ -6542,8 +7014,14 @@
       <c r="C129" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D129" s="41" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E129" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="18" t="s">
         <v>1103</v>
       </c>
@@ -6553,8 +7031,14 @@
       <c r="C130" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D130" s="41" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E130" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="18" t="s">
         <v>1104</v>
       </c>
@@ -6564,8 +7048,14 @@
       <c r="C131" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D131" s="41" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E131" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="18" t="s">
         <v>1105</v>
       </c>
@@ -6575,8 +7065,14 @@
       <c r="C132" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D132" s="41" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E132" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="18" t="s">
         <v>1106</v>
       </c>
@@ -6586,8 +7082,14 @@
       <c r="C133" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D133" s="41" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E133" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="18" t="s">
         <v>1107</v>
       </c>
@@ -6597,8 +7099,14 @@
       <c r="C134" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D134" s="41" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E134" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="18" t="s">
         <v>1108</v>
       </c>
@@ -6608,8 +7116,14 @@
       <c r="C135" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D135" s="41" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E135" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="18" t="s">
         <v>1109</v>
       </c>
@@ -6619,8 +7133,14 @@
       <c r="C136" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D136" s="41" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E136" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="18" t="s">
         <v>1110</v>
       </c>
@@ -6630,8 +7150,14 @@
       <c r="C137" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D137" s="41" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E137" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="18" t="s">
         <v>1111</v>
       </c>
@@ -6641,8 +7167,14 @@
       <c r="C138" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D138" s="41" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E138" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="18" t="s">
         <v>1112</v>
       </c>
@@ -6652,8 +7184,14 @@
       <c r="C139" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D139" s="41" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E139" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="18" t="s">
         <v>1113</v>
       </c>
@@ -6663,8 +7201,14 @@
       <c r="C140" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D140" s="41" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E140" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="18" t="s">
         <v>1114</v>
       </c>
@@ -6674,8 +7218,14 @@
       <c r="C141" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D141" s="41" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E141" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="18" t="s">
         <v>1115</v>
       </c>
@@ -6685,8 +7235,14 @@
       <c r="C142" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D142" s="41" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E142" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="18" t="s">
         <v>1116</v>
       </c>
@@ -6696,8 +7252,14 @@
       <c r="C143" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D143" s="41" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E143" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="18" t="s">
         <v>1117</v>
       </c>
@@ -6707,8 +7269,14 @@
       <c r="C144" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D144" s="41" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E144" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="18" t="s">
         <v>1118</v>
       </c>
@@ -6718,8 +7286,14 @@
       <c r="C145" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D145" s="41" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E145" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="18" t="s">
         <v>1119</v>
       </c>
@@ -6729,8 +7303,14 @@
       <c r="C146" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D146" s="41" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E146" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="18" t="s">
         <v>1120</v>
       </c>
@@ -6740,8 +7320,14 @@
       <c r="C147" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D147" s="41" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E147" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="18" t="s">
         <v>1121</v>
       </c>
@@ -6751,8 +7337,14 @@
       <c r="C148" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D148" s="41" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E148" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="18" t="s">
         <v>1122</v>
       </c>
@@ -6762,8 +7354,14 @@
       <c r="C149" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D149" s="41" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E149" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="18" t="s">
         <v>1123</v>
       </c>
@@ -6773,8 +7371,14 @@
       <c r="C150" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D150" s="41" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E150" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="18" t="s">
         <v>1124</v>
       </c>
@@ -6784,8 +7388,14 @@
       <c r="C151" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D151" s="41" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E151" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="18" t="s">
         <v>1125</v>
       </c>
@@ -6795,8 +7405,14 @@
       <c r="C152" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D152" s="41" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E152" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="18" t="s">
         <v>1126</v>
       </c>
@@ -6806,8 +7422,14 @@
       <c r="C153" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D153" s="41" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E153" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="18" t="s">
         <v>1127</v>
       </c>
@@ -6817,8 +7439,14 @@
       <c r="C154" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D154" s="41" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E154" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="18" t="s">
         <v>1128</v>
       </c>
@@ -6828,8 +7456,14 @@
       <c r="C155" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D155" s="41" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E155" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" s="18" t="s">
         <v>1129</v>
       </c>
@@ -6839,8 +7473,14 @@
       <c r="C156" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D156" s="41" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E156" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="18" t="s">
         <v>1130</v>
       </c>
@@ -6850,8 +7490,14 @@
       <c r="C157" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D157" s="41" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E157" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="18" t="s">
         <v>1131</v>
       </c>
@@ -6861,8 +7507,14 @@
       <c r="C158" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D158" s="41" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E158" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="18" t="s">
         <v>1132</v>
       </c>
@@ -6872,8 +7524,14 @@
       <c r="C159" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D159" s="41" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E159" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="18" t="s">
         <v>1133</v>
       </c>
@@ -6883,8 +7541,14 @@
       <c r="C160" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D160" s="41" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E160" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="18" t="s">
         <v>1134</v>
       </c>
@@ -6894,8 +7558,14 @@
       <c r="C161" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D161" s="41" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E161" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="18" t="s">
         <v>1135</v>
       </c>
@@ -6905,8 +7575,14 @@
       <c r="C162" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D162" s="41" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E162" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="18" t="s">
         <v>1136</v>
       </c>
@@ -6916,8 +7592,14 @@
       <c r="C163" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D163" s="41" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E163" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="18" t="s">
         <v>1137</v>
       </c>
@@ -6927,8 +7609,14 @@
       <c r="C164" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D164" s="41" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E164" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="18" t="s">
         <v>1138</v>
       </c>
@@ -6938,8 +7626,14 @@
       <c r="C165" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D165" s="41" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E165" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="18" t="s">
         <v>1139</v>
       </c>
@@ -6949,8 +7643,14 @@
       <c r="C166" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D166" s="41" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E166" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="18" t="s">
         <v>1140</v>
       </c>
@@ -6960,8 +7660,14 @@
       <c r="C167" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D167" s="41" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E167" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="18" t="s">
         <v>1141</v>
       </c>
@@ -6971,8 +7677,14 @@
       <c r="C168" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D168" s="41" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E168" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="18" t="s">
         <v>1142</v>
       </c>
@@ -6982,8 +7694,14 @@
       <c r="C169" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D169" s="41" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E169" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="18" t="s">
         <v>1143</v>
       </c>
@@ -6993,8 +7711,14 @@
       <c r="C170" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D170" s="41" t="s">
+        <v>1504</v>
+      </c>
+      <c r="E170" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="18" t="s">
         <v>1144</v>
       </c>
@@ -7004,8 +7728,14 @@
       <c r="C171" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D171" s="41" t="s">
+        <v>1504</v>
+      </c>
+      <c r="E171" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="18" t="s">
         <v>1145</v>
       </c>
@@ -7015,8 +7745,14 @@
       <c r="C172" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D172" s="41" t="s">
+        <v>1504</v>
+      </c>
+      <c r="E172" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="18" t="s">
         <v>1146</v>
       </c>
@@ -7026,8 +7762,14 @@
       <c r="C173" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D173" s="41" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E173" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="18" t="s">
         <v>1147</v>
       </c>
@@ -7037,8 +7779,14 @@
       <c r="C174" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D174" s="41" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E174" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="18" t="s">
         <v>1148</v>
       </c>
@@ -7048,8 +7796,14 @@
       <c r="C175" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D175" s="41" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E175" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="18" t="s">
         <v>1149</v>
       </c>
@@ -7059,8 +7813,14 @@
       <c r="C176" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D176" s="41" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E176" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="18" t="s">
         <v>1150</v>
       </c>
@@ -7070,8 +7830,14 @@
       <c r="C177" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D177" s="41" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E177" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="18" t="s">
         <v>1151</v>
       </c>
@@ -7081,8 +7847,14 @@
       <c r="C178" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D178" s="41" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E178" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="18" t="s">
         <v>1152</v>
       </c>
@@ -7092,8 +7864,14 @@
       <c r="C179" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D179" s="41" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E179" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="18" t="s">
         <v>1153</v>
       </c>
@@ -7103,8 +7881,14 @@
       <c r="C180" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D180" s="41" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E180" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="18" t="s">
         <v>1154</v>
       </c>
@@ -7114,8 +7898,14 @@
       <c r="C181" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D181" s="41" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E181" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="18" t="s">
         <v>1155</v>
       </c>
@@ -7125,8 +7915,14 @@
       <c r="C182" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D182" s="41" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E182" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="18" t="s">
         <v>1156</v>
       </c>
@@ -7136,8 +7932,14 @@
       <c r="C183" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D183" s="41" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E183" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="18" t="s">
         <v>1157</v>
       </c>
@@ -7147,8 +7949,14 @@
       <c r="C184" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D184" s="41" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E184" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="18" t="s">
         <v>1158</v>
       </c>
@@ -7158,8 +7966,14 @@
       <c r="C185" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D185" s="41" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E185" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="18" t="s">
         <v>1159</v>
       </c>
@@ -7169,8 +7983,14 @@
       <c r="C186" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D186" s="41" t="s">
+        <v>1510</v>
+      </c>
+      <c r="E186" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="18" t="s">
         <v>1160</v>
       </c>
@@ -7180,8 +8000,14 @@
       <c r="C187" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D187" s="41" t="s">
+        <v>1510</v>
+      </c>
+      <c r="E187" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="18" t="s">
         <v>1161</v>
       </c>
@@ -7191,8 +8017,14 @@
       <c r="C188" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D188" s="41" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E188" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="18" t="s">
         <v>1162</v>
       </c>
@@ -7202,8 +8034,14 @@
       <c r="C189" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D189" s="41" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E189" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="18" t="s">
         <v>1163</v>
       </c>
@@ -7213,8 +8051,14 @@
       <c r="C190" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D190" s="41" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E190" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="18" t="s">
         <v>1164</v>
       </c>
@@ -7224,8 +8068,14 @@
       <c r="C191" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D191" s="41" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E191" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="18" t="s">
         <v>1165</v>
       </c>
@@ -7235,8 +8085,14 @@
       <c r="C192" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D192" s="41" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E192" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="18" t="s">
         <v>1166</v>
       </c>
@@ -7246,50 +8102,56 @@
       <c r="C193" s="18" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D193" s="41" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E193" s="39" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="33"/>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="33"/>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="33"/>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="33"/>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="33"/>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="33"/>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="33"/>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="33"/>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="33"/>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="33"/>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" s="33"/>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" s="33"/>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="33"/>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="33"/>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="33"/>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.2">
